--- a/business_report_forms/005_personnel_activity_report_form_for_federal_grants--business_report_forms.xlsx
+++ b/business_report_forms/005_personnel_activity_report_form_for_federal_grants--business_report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,18 +520,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>project_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Personnel Activity Report Form For Federal Grants</t>
+          <t>Project Name</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>project_description</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -577,30 +577,30 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>assigned_tool</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Form ID</t>
+          <t>Assigned Tool</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,18 +612,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>project_completed</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>Project Completed</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -646,14 +646,14 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -666,11 +666,7 @@
           <t>Form Description</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>A Personnel Activity Report Form for Federal Grants is a template designed for seamless, systematic tracking of federally funded projects. Perfect for grant administrators, this intuitive template aids in ensuring accurate time and effort reporting. Simplify your grant management process!</t>
-        </is>
-      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -680,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>form_id</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Form ID</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -703,48 +699,46 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>is_federally_funded</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Is Federally Funded</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>repeat_occurrence</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Form ID</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>67333</v>
-      </c>
+          <t>Repeat Occurrence</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -756,156 +750,41 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>assigned_tool_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>Assigned Tool 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>output_file</t>
+          <t>category_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Output File</t>
+          <t>Category 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>form_description</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Form Description</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>form_title</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Assigned Tool</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>output_file</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Output File</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -920,10 +799,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
@@ -987,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>chatjimmy</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>chatjimmy</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1004,19 +883,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>project_completed_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1033,7 +912,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>project_completed_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1050,7 +929,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>is_federally_funded_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1067,7 +946,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>is_federally_funded_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1084,7 +963,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>repeat_occurrence_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1101,7 +980,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>repeat_occurrence_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1118,7 +997,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>assigned_tool_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1135,7 +1014,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>assigned_tool_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1144,6 +1023,40 @@
         </is>
       </c>
       <c r="C13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>category_2_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>category_2_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
